--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/ImportGeneralExcel.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/ImportGeneralExcel.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Lương Cố Định</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Các Khoản Phát Sinh (Tăng / Giảm)</t>
   </si>
   <si>
     <t>Employee_ID</t>
@@ -23,18 +23,15 @@
     <t>SalaryComponent</t>
   </si>
   <si>
-    <t>Fromdate</t>
+    <t>Year_</t>
+  </si>
+  <si>
+    <t>Month_</t>
   </si>
   <si>
     <t>Amount</t>
   </si>
   <si>
-    <t>Todate</t>
-  </si>
-  <si>
-    <t>InsertSource</t>
-  </si>
-  <si>
     <t>Remark</t>
   </si>
   <si>
@@ -47,13 +44,10 @@
     <t>Tiền</t>
   </si>
   <si>
-    <t>Từ ngày</t>
-  </si>
-  <si>
-    <t>Đến ngày</t>
-  </si>
-  <si>
-    <t>Nguồn nhập</t>
+    <t>Năm</t>
+  </si>
+  <si>
+    <t>Tháng</t>
   </si>
   <si>
     <t>Ghi chú</t>
@@ -127,16 +121,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A3:G10"/>
+  <dimension ref="A3:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.675158909389" customWidth="1"/>
     <col min="2" max="2" width="18.009886605399" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.79262597220285" customWidth="1"/>
-    <col min="6" max="6" width="12.3605194091797" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -169,6 +162,9 @@
       <c r="D5" s="0" t="s">
         <v>3</v>
       </c>
+      <c r="E5" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" hidden="1">
       <c r="A6" s="0" t="s">
@@ -178,42 +174,36 @@
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="0" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/ImportGeneralExcel.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/ImportGeneralExcel.xlsx
@@ -12,45 +12,93 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Các Khoản Phát Sinh (Tăng / Giảm)</t>
-  </si>
-  <si>
-    <t>Employee_ID</t>
-  </si>
-  <si>
-    <t>SalaryComponent</t>
-  </si>
-  <si>
-    <t>Year_</t>
-  </si>
-  <si>
-    <t>Month_</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Remark</t>
-  </si>
-  <si>
-    <t>Mã nhân viên</t>
-  </si>
-  <si>
-    <t>Thành phần lương</t>
-  </si>
-  <si>
-    <t>Tiền</t>
-  </si>
-  <si>
-    <t>Năm</t>
-  </si>
-  <si>
-    <t>Tháng</t>
-  </si>
-  <si>
-    <t>Ghi chú</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Tạo/Điều Chỉnh Bộ Phận</t>
+  </si>
+  <si>
+    <t>SectionCode</t>
+  </si>
+  <si>
+    <t>DepartmentCode</t>
+  </si>
+  <si>
+    <t>Factory_ID</t>
+  </si>
+  <si>
+    <t>SectionName_VN</t>
+  </si>
+  <si>
+    <t>SectionName_EN</t>
+  </si>
+  <si>
+    <t>SectionName_KR</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>CaMacDinh</t>
+  </si>
+  <si>
+    <t>GioiHanTangCaMacDinh</t>
+  </si>
+  <si>
+    <t>AnnualLeaveDays</t>
+  </si>
+  <si>
+    <t>ContractFlow</t>
+  </si>
+  <si>
+    <t>OrderBy</t>
+  </si>
+  <si>
+    <t>JobCode</t>
+  </si>
+  <si>
+    <t>Group_</t>
+  </si>
+  <si>
+    <t>Mã Bộ phận</t>
+  </si>
+  <si>
+    <t>Bộ phận</t>
+  </si>
+  <si>
+    <t>Xưởng</t>
+  </si>
+  <si>
+    <t>Tên mã bộ phận (VN)</t>
+  </si>
+  <si>
+    <t>Tên mã bộ phận (EN)</t>
+  </si>
+  <si>
+    <t>Tên mã bộ phận (KR)</t>
+  </si>
+  <si>
+    <t>Trực tiếp</t>
+  </si>
+  <si>
+    <t>Ca mặc định</t>
+  </si>
+  <si>
+    <t>Giới hạn tăng ca mặc định</t>
+  </si>
+  <si>
+    <t>Số ngày phép năm</t>
+  </si>
+  <si>
+    <t>Luồng hợp đồng</t>
+  </si>
+  <si>
+    <t>Số thứ tự</t>
+  </si>
+  <si>
+    <t>Mã công việc</t>
+  </si>
+  <si>
+    <t>Nhóm</t>
   </si>
 </sst>
 </file>
@@ -121,15 +169,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A3:F10"/>
+  <dimension ref="A3:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.675158909389" customWidth="1"/>
-    <col min="2" max="2" width="18.009886605399" customWidth="1"/>
+    <col min="1" max="1" width="12.2490059988839" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.3966979980469" customWidth="1"/>
+    <col min="5" max="5" width="20.1736689976283" customWidth="1"/>
+    <col min="6" max="6" width="20.0959167480469" customWidth="1"/>
+    <col min="7" max="7" width="9.55936704363142" customWidth="1"/>
+    <col min="8" max="8" width="12.394280569894" customWidth="1"/>
+    <col min="9" max="9" width="24.7948564801897" customWidth="1"/>
+    <col min="10" max="10" width="17.864612034389" customWidth="1"/>
+    <col min="11" max="11" width="16.0517392839704" customWidth="1"/>
+    <col min="12" max="12" width="10.0177001953125" customWidth="1"/>
+    <col min="13" max="13" width="13.1257727486747" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -159,11 +215,8 @@
       <c r="B5" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" s="0" t="s">
         <v>3</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="6" hidden="1">
@@ -174,36 +227,84 @@
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="0" t="s">
         <v>5</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>4</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>6</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/ImportGeneralExcel.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/ImportGeneralExcel.xlsx
@@ -12,93 +12,123 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>Tạo/Điều Chỉnh Bộ Phận</t>
-  </si>
-  <si>
-    <t>SectionCode</t>
-  </si>
-  <si>
-    <t>DepartmentCode</t>
-  </si>
-  <si>
-    <t>Factory_ID</t>
-  </si>
-  <si>
-    <t>SectionName_VN</t>
-  </si>
-  <si>
-    <t>SectionName_EN</t>
-  </si>
-  <si>
-    <t>SectionName_KR</t>
-  </si>
-  <si>
-    <t>Direct</t>
-  </si>
-  <si>
-    <t>CaMacDinh</t>
-  </si>
-  <si>
-    <t>GioiHanTangCaMacDinh</t>
-  </si>
-  <si>
-    <t>AnnualLeaveDays</t>
-  </si>
-  <si>
-    <t>ContractFlow</t>
-  </si>
-  <si>
-    <t>OrderBy</t>
-  </si>
-  <si>
-    <t>JobCode</t>
-  </si>
-  <si>
-    <t>Group_</t>
-  </si>
-  <si>
-    <t>Mã Bộ phận</t>
-  </si>
-  <si>
-    <t>Bộ phận</t>
-  </si>
-  <si>
-    <t>Xưởng</t>
-  </si>
-  <si>
-    <t>Tên mã bộ phận (VN)</t>
-  </si>
-  <si>
-    <t>Tên mã bộ phận (EN)</t>
-  </si>
-  <si>
-    <t>Tên mã bộ phận (KR)</t>
-  </si>
-  <si>
-    <t>Trực tiếp</t>
-  </si>
-  <si>
-    <t>Ca mặc định</t>
-  </si>
-  <si>
-    <t>Giới hạn tăng ca mặc định</t>
-  </si>
-  <si>
-    <t>Số ngày phép năm</t>
-  </si>
-  <si>
-    <t>Luồng hợp đồng</t>
-  </si>
-  <si>
-    <t>Số thứ tự</t>
-  </si>
-  <si>
-    <t>Mã công việc</t>
-  </si>
-  <si>
-    <t>Nhóm</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+  <si>
+    <t>frmNhapDuLieuCong</t>
+  </si>
+  <si>
+    <t>Employee_ID</t>
+  </si>
+  <si>
+    <t>Thang</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>LoaiGio</t>
+  </si>
+  <si>
+    <t>Day1</t>
+  </si>
+  <si>
+    <t>Day2</t>
+  </si>
+  <si>
+    <t>Day3</t>
+  </si>
+  <si>
+    <t>Day4</t>
+  </si>
+  <si>
+    <t>Day5</t>
+  </si>
+  <si>
+    <t>Day6</t>
+  </si>
+  <si>
+    <t>Day7</t>
+  </si>
+  <si>
+    <t>Day8</t>
+  </si>
+  <si>
+    <t>Day9</t>
+  </si>
+  <si>
+    <t>Day10</t>
+  </si>
+  <si>
+    <t>Day11</t>
+  </si>
+  <si>
+    <t>Day12</t>
+  </si>
+  <si>
+    <t>Day13</t>
+  </si>
+  <si>
+    <t>Day14</t>
+  </si>
+  <si>
+    <t>Day15</t>
+  </si>
+  <si>
+    <t>Day16</t>
+  </si>
+  <si>
+    <t>Day17</t>
+  </si>
+  <si>
+    <t>Day18</t>
+  </si>
+  <si>
+    <t>Day19</t>
+  </si>
+  <si>
+    <t>Day20</t>
+  </si>
+  <si>
+    <t>Day21</t>
+  </si>
+  <si>
+    <t>Day22</t>
+  </si>
+  <si>
+    <t>Day23</t>
+  </si>
+  <si>
+    <t>Day24</t>
+  </si>
+  <si>
+    <t>Day25</t>
+  </si>
+  <si>
+    <t>Day26</t>
+  </si>
+  <si>
+    <t>Day27</t>
+  </si>
+  <si>
+    <t>Day28</t>
+  </si>
+  <si>
+    <t>Day29</t>
+  </si>
+  <si>
+    <t>Day30</t>
+  </si>
+  <si>
+    <t>Day31</t>
+  </si>
+  <si>
+    <t>Mã nhân viên</t>
+  </si>
+  <si>
+    <t>Tháng:</t>
+  </si>
+  <si>
+    <t>Năm:</t>
   </si>
 </sst>
 </file>
@@ -169,23 +199,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A3:N10"/>
+  <dimension ref="A3:AI10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.2490059988839" customWidth="1"/>
+    <col min="1" max="1" width="13.675158909389" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="20.3966979980469" customWidth="1"/>
-    <col min="5" max="5" width="20.1736689976283" customWidth="1"/>
-    <col min="6" max="6" width="20.0959167480469" customWidth="1"/>
-    <col min="7" max="7" width="9.55936704363142" customWidth="1"/>
-    <col min="8" max="8" width="12.394280569894" customWidth="1"/>
-    <col min="9" max="9" width="24.7948564801897" customWidth="1"/>
-    <col min="10" max="10" width="17.864612034389" customWidth="1"/>
-    <col min="11" max="11" width="16.0517392839704" customWidth="1"/>
-    <col min="12" max="12" width="10.0177001953125" customWidth="1"/>
-    <col min="13" max="13" width="13.1257727486747" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" customWidth="1"/>
     <col min="14" max="14" width="9.140625" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" customWidth="1"/>
+    <col min="25" max="25" width="9.140625" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" customWidth="1"/>
+    <col min="27" max="27" width="9.140625" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" customWidth="1"/>
+    <col min="29" max="29" width="9.140625" customWidth="1"/>
+    <col min="30" max="30" width="9.140625" customWidth="1"/>
+    <col min="31" max="31" width="9.140625" customWidth="1"/>
+    <col min="32" max="32" width="9.140625" customWidth="1"/>
+    <col min="33" max="33" width="9.140625" customWidth="1"/>
+    <col min="34" max="34" width="9.140625" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -218,6 +269,9 @@
       <c r="C5" s="0" t="s">
         <v>3</v>
       </c>
+      <c r="D5" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" hidden="1">
       <c r="A6" s="0" t="s">
@@ -262,49 +316,175 @@
       <c r="N6" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="O6" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="P6" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="R6" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="S6" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="T6" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="U6" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="V6" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="W6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="X6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA6" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC6" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD6" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE6" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI6" s="0" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="P10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="Q10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="R10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="T10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="U10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="V10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="W10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="X10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="Y10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="Z10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="AA10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="AB10" s="3" t="s">
         <v>28</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
